--- a/bylines/commentaries/retail-2026-05-22.xlsx
+++ b/bylines/commentaries/retail-2026-05-22.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jayzh\projects\macro-research-department\bylines\commentaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52935C93-884C-42A0-9725-FF0DE1EE07C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C8151C-A5A4-469C-8240-D080154151AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -744,7 +744,7 @@
                   <c:v>107.41243106275154</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>108.80906245342076</c:v>
+                  <c:v>108.31122372931883</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -868,7 +868,7 @@
                   <c:v>103.52242160100786</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>103.85099935305935</c:v>
+                  <c:v>101.93911947972352</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7732,38 +7732,38 @@
         <v>46082</v>
       </c>
       <c r="B61" s="5">
-        <v>73000</v>
+        <v>72666</v>
       </c>
       <c r="C61" s="5">
-        <v>61000</v>
+        <v>59877</v>
       </c>
       <c r="D61" s="4">
         <f t="shared" ref="D61" si="10">IFERROR((B61/B60-1)*100,"")</f>
-        <v>1.300251169115918</v>
+        <v>0.83676782815036432</v>
       </c>
       <c r="E61" s="4">
         <f t="shared" ref="E61" si="11">IFERROR((C61/C60-1)*100,"")</f>
-        <v>0.31739766803164926</v>
+        <v>-1.5294291775617919</v>
       </c>
       <c r="F61" s="4">
         <f t="shared" ref="F61" si="12">IFERROR(D61-E61,"")</f>
-        <v>0.98285350108426872</v>
+        <v>2.3661970057121562</v>
       </c>
       <c r="G61" s="4">
         <f t="shared" ref="G61" si="13">IFERROR((B61/B49-1)*100,"")</f>
-        <v>3.8850149423651725</v>
+        <v>3.4097054219439205</v>
       </c>
       <c r="H61" s="4">
         <f t="shared" ref="H61" si="14">IFERROR((C61/C49-1)*100,"")</f>
-        <v>1.2397722934957667</v>
+        <v>-0.62403531774350984</v>
       </c>
       <c r="J61">
         <f t="shared" ref="J61" si="15">B61/B$35*100</f>
-        <v>108.80906245342076</v>
+        <v>108.31122372931883</v>
       </c>
       <c r="K61">
         <f t="shared" ref="K61" si="16">C61/C$35*100</f>
-        <v>103.85099935305935</v>
+        <v>101.93911947972352</v>
       </c>
     </row>
   </sheetData>
